--- a/csv/model/DIC/formula_DIC_AB.xlsx
+++ b/csv/model/DIC/formula_DIC_AB.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3624" yWindow="2148" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1" iterate="1" calcOnSave="0"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" calcOnSave="0"/>
 </workbook>
 </file>
 
@@ -440,12 +440,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:X302"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -757,7 +757,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -837,7 +837,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -917,7 +917,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M9" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M10" t="n">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M12" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M13" t="n">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M14" t="n">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M16" t="n">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M17" t="n">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M18" t="n">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M20" t="n">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M21" t="n">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M22" t="n">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M24" t="n">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M25" t="n">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M26" t="n">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M28" t="n">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M29" t="n">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M30" t="n">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M32" t="n">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M33" t="n">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M34" t="n">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M36" t="n">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M37" t="n">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M38" t="n">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M40" t="n">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M41" t="n">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M42" t="n">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M44" t="n">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M45" t="n">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M46" t="n">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M48" t="n">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M49" t="n">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M50" t="n">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M52" t="n">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M53" t="n">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M54" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M56" t="n">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M57" t="n">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M58" t="n">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M60" t="n">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M61" t="n">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M62" t="n">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M64" t="n">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M65" t="n">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M66" t="n">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M68" t="n">
@@ -5957,7 +5957,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M69" t="n">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M70" t="n">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M72" t="n">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M73" t="n">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M74" t="n">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M76" t="n">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M77" t="n">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M78" t="n">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M80" t="n">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M81" t="n">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M82" t="n">
@@ -7092,7 +7092,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M84" t="n">
@@ -7257,7 +7257,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M85" t="n">
@@ -7337,7 +7337,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M86" t="n">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M88" t="n">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M89" t="n">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M90" t="n">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M92" t="n">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M93" t="n">
@@ -7987,7 +7987,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M94" t="n">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M96" t="n">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M97" t="n">
@@ -8312,7 +8312,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M98" t="n">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M100" t="n">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M101" t="n">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M102" t="n">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -8802,7 +8802,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M104" t="n">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M105" t="n">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M106" t="n">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -9127,7 +9127,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M108" t="n">
@@ -9207,7 +9207,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M109" t="n">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M110" t="n">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M112" t="n">
@@ -9532,7 +9532,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M113" t="n">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M114" t="n">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -9777,7 +9777,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M116" t="n">
@@ -9857,7 +9857,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M117" t="n">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M118" t="n">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M120" t="n">
@@ -10182,7 +10182,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M121" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M122" t="n">
@@ -10342,7 +10342,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -10427,7 +10427,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M124" t="n">
@@ -10507,7 +10507,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M125" t="n">
@@ -10587,7 +10587,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M126" t="n">
@@ -10667,7 +10667,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M128" t="n">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M129" t="n">
@@ -10912,7 +10912,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M130" t="n">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M132" t="n">
@@ -11157,7 +11157,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M133" t="n">
@@ -11237,7 +11237,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M134" t="n">
@@ -11317,7 +11317,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -11402,7 +11402,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M136" t="n">
@@ -11482,7 +11482,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M137" t="n">
@@ -11562,7 +11562,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M138" t="n">
@@ -11642,7 +11642,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M140" t="n">
@@ -11807,7 +11807,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M141" t="n">
@@ -11887,7 +11887,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M142" t="n">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M144" t="n">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M145" t="n">
@@ -12212,7 +12212,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M146" t="n">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -12377,7 +12377,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M148" t="n">
@@ -12457,7 +12457,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M149" t="n">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M150" t="n">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -12702,7 +12702,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M152" t="n">
@@ -12782,7 +12782,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M153" t="n">
@@ -12862,7 +12862,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M154" t="n">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -13027,7 +13027,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M156" t="n">
@@ -13107,7 +13107,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M157" t="n">
@@ -13187,7 +13187,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M158" t="n">
@@ -13267,7 +13267,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M160" t="n">
@@ -13432,7 +13432,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M161" t="n">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M162" t="n">
@@ -13592,7 +13592,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -13677,7 +13677,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M164" t="n">
@@ -13757,7 +13757,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M165" t="n">
@@ -13837,7 +13837,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M166" t="n">
@@ -13917,7 +13917,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -14002,7 +14002,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M168" t="n">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M169" t="n">
@@ -14162,7 +14162,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M170" t="n">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -14327,7 +14327,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M172" t="n">
@@ -14407,7 +14407,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M173" t="n">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M174" t="n">
@@ -14567,7 +14567,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -14652,7 +14652,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M176" t="n">
@@ -14732,7 +14732,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M177" t="n">
@@ -14812,7 +14812,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M178" t="n">
@@ -14892,7 +14892,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -14977,7 +14977,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M180" t="n">
@@ -15057,7 +15057,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M181" t="n">
@@ -15137,7 +15137,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M182" t="n">
@@ -15217,7 +15217,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -15302,7 +15302,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M184" t="n">
@@ -15382,7 +15382,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M185" t="n">
@@ -15462,7 +15462,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M186" t="n">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -15627,7 +15627,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M188" t="n">
@@ -15707,7 +15707,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M189" t="n">
@@ -15787,7 +15787,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M190" t="n">
@@ -15867,7 +15867,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -15952,7 +15952,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M192" t="n">
@@ -16032,7 +16032,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M193" t="n">
@@ -16112,7 +16112,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M194" t="n">
@@ -16192,7 +16192,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -16277,7 +16277,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M196" t="n">
@@ -16357,7 +16357,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M197" t="n">
@@ -16437,7 +16437,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M198" t="n">
@@ -16517,7 +16517,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -16602,7 +16602,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M200" t="n">
@@ -16682,7 +16682,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M201" t="n">
@@ -16762,7 +16762,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M202" t="n">
@@ -16842,7 +16842,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -16927,7 +16927,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M204" t="n">
@@ -17007,7 +17007,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M205" t="n">
@@ -17087,7 +17087,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M206" t="n">
@@ -17167,7 +17167,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -17252,7 +17252,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M208" t="n">
@@ -17332,7 +17332,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M209" t="n">
@@ -17412,7 +17412,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M210" t="n">
@@ -17492,7 +17492,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -17577,7 +17577,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M212" t="n">
@@ -17657,7 +17657,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M213" t="n">
@@ -17737,7 +17737,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M214" t="n">
@@ -17817,7 +17817,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -17902,7 +17902,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M216" t="n">
@@ -17982,7 +17982,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M217" t="n">
@@ -18062,7 +18062,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M218" t="n">
@@ -18142,7 +18142,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -18227,7 +18227,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M220" t="n">
@@ -18307,7 +18307,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M221" t="n">
@@ -18387,7 +18387,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M222" t="n">
@@ -18467,7 +18467,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -18552,7 +18552,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M224" t="n">
@@ -18632,7 +18632,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M225" t="n">
@@ -18712,7 +18712,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M226" t="n">
@@ -18792,7 +18792,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M228" t="n">
@@ -18957,7 +18957,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M229" t="n">
@@ -19037,7 +19037,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M230" t="n">
@@ -19117,7 +19117,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -19202,7 +19202,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M232" t="n">
@@ -19282,7 +19282,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M233" t="n">
@@ -19362,7 +19362,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M234" t="n">
@@ -19442,7 +19442,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -19527,7 +19527,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M236" t="n">
@@ -19607,7 +19607,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M237" t="n">
@@ -19687,7 +19687,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M238" t="n">
@@ -19767,7 +19767,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -19852,7 +19852,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M240" t="n">
@@ -19932,7 +19932,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M241" t="n">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M242" t="n">
@@ -20092,7 +20092,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -20177,7 +20177,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M244" t="n">
@@ -20257,7 +20257,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M245" t="n">
@@ -20337,7 +20337,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M246" t="n">
@@ -20417,7 +20417,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -20502,7 +20502,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M248" t="n">
@@ -20582,7 +20582,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M249" t="n">
@@ -20662,7 +20662,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M250" t="n">
@@ -20742,7 +20742,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -20827,7 +20827,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M252" t="n">
@@ -20907,7 +20907,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M253" t="n">
@@ -20987,7 +20987,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M254" t="n">
@@ -21067,7 +21067,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -21152,7 +21152,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M256" t="n">
@@ -21232,7 +21232,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M257" t="n">
@@ -21312,7 +21312,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M258" t="n">
@@ -21392,7 +21392,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -21477,7 +21477,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M260" t="n">
@@ -21557,7 +21557,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M261" t="n">
@@ -21637,7 +21637,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M262" t="n">
@@ -21717,7 +21717,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -21802,7 +21802,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M264" t="n">
@@ -21882,7 +21882,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M265" t="n">
@@ -21962,7 +21962,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M266" t="n">
@@ -22042,7 +22042,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -22127,7 +22127,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M268" t="n">
@@ -22207,7 +22207,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M269" t="n">
@@ -22287,7 +22287,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M270" t="n">
@@ -22367,7 +22367,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -22452,7 +22452,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M272" t="n">
@@ -22532,7 +22532,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M273" t="n">
@@ -22612,7 +22612,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M274" t="n">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M276" t="n">
@@ -22857,7 +22857,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M277" t="n">
@@ -22937,7 +22937,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M278" t="n">
@@ -23017,7 +23017,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
@@ -23102,7 +23102,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M280" t="n">
@@ -23182,7 +23182,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M281" t="n">
@@ -23262,7 +23262,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M282" t="n">
@@ -23342,7 +23342,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
@@ -23427,7 +23427,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M284" t="n">
@@ -23507,7 +23507,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M285" t="n">
@@ -23587,7 +23587,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M286" t="n">
@@ -23667,7 +23667,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -23752,7 +23752,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M288" t="n">
@@ -23832,7 +23832,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M289" t="n">
@@ -23912,7 +23912,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M290" t="n">
@@ -23992,7 +23992,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
@@ -24077,7 +24077,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M292" t="n">
@@ -24157,7 +24157,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M293" t="n">
@@ -24237,7 +24237,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M294" t="n">
@@ -24317,7 +24317,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
@@ -24402,7 +24402,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M296" t="n">
@@ -24482,7 +24482,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M297" t="n">
@@ -24562,7 +24562,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M298" t="n">
@@ -24642,7 +24642,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>DIC_initial</t>
+          <t>dic_initial</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
@@ -24727,7 +24727,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>DIC_slope</t>
+          <t>dic_slope</t>
         </is>
       </c>
       <c r="M300" t="n">
@@ -24807,7 +24807,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>DIC_x50</t>
+          <t>dic_x50</t>
         </is>
       </c>
       <c r="M301" t="n">
@@ -24887,7 +24887,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>DIC_min</t>
+          <t>dic_min</t>
         </is>
       </c>
       <c r="M302" t="n">
